--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prince Central 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -711,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -807,7 +665,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -853,7 +711,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -949,7 +807,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -995,7 +853,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1429,7 +1287,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1667,7 +1525,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1863,7 +1721,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1959,7 +1817,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2005,7 +1863,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2101,7 +1959,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2193,7 +2051,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2331,7 +2189,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2427,7 +2285,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2519,7 +2377,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2565,7 +2423,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2703,7 +2561,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2799,7 +2657,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2891,7 +2749,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3075,7 +2933,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3447,7 +3305,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3543,7 +3401,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3635,7 +3493,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3819,7 +3677,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4053,7 +3911,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4191,7 +4049,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4379,7 +4237,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4563,7 +4421,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4935,7 +4793,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5433,1083 +5291,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Prince Central - Prince Central 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>101 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>29 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 834呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (4+房)
-$6,008万
-$44,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 869呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 685呎 (3房)
-$2,460万
-$35,907/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 890呎 (4+房)
-$3,218万
-$36,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="18" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
-      <c r="I7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 871呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 344呎 (1房)
-$1,075万
-$31,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 891呎 (4+房)
-$3,150万
-$35,354/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,388万
-$31,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$1,148万
-$37,901/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,283万
-$37,181/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 254呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>F | 624呎 (3房)
-$2,642万
-$42,335/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>G | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$971万
-$31,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,258万
-$36,452/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 254呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>F | 624呎 (3房)
-$2,587万
-$41,460/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>G | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,312万
-$30,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$962万
-$31,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,060万
-$30,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 254呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 624呎 (3房)
-$2,132万
-$34,173/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>G | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,302万
-$29,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$946万
-$31,106/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,229万
-$35,632/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>E | 254呎 (开放式)
-$941万
-$37,051/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 624呎 (3房)
-$2,062万
-$33,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>G | 266呎 (开放式)
-$973万
-$36,594/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,362万
-$31,238/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$924万
-$30,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,204万
-$34,899/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$899万
-$35,805/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,032万
-$30,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,042万
-$30,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$956万
-$35,955/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,506万
-$34,534/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$896万
-$29,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,198万
-$34,728/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$890万
-$35,462/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,204万
-$35,630/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,034万
-$30,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$949万
-$35,669/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,273万
-$29,208/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$893万
-$29,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,191万
-$34,522/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$880万
-$35,052/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,201万
-$35,527/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,213万
-$35,262/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$941万
-$35,383/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,498万
-$34,362/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$893万
-$29,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,191万
-$34,522/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$880万
-$35,052/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,201万
-$35,527/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 343呎 (1房)
-$1,031万
-$30,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$941万
-$35,383/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,483万
-$34,021/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$886万
-$29,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,184万
-$34,316/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$858万
-$34,195/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,015万
-$30,017/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,206万
-$35,047/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$928万
-$34,887/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,476万
-$33,851/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$883万
-$29,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,176万
-$34,099/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$847万
-$33,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,190万
-$35,207/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 343呎 (1房)
-$1,022万
-$29,787/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$921万
-$34,639/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 436呎 (2房)
-$1,468万
-$33,679/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$880万
-$29,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 345呎 (1房)
-$1,174万
-$34,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$829万
-$33,032/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,165万
-$34,462/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,176万
-$34,198/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$893万
-$33,564/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 274呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 283呎 (1房)
-$1,103万
-$38,965/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 251呎 (开放式)
-$817万
-$32,562/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>F | 338呎 (1房)
-$1,150万
-$34,012/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>G | 344呎 (1房)
-$1,161万
-$33,750/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>H | 266呎 (开放式)
-$919万
-$34,538/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prince Central" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +234,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5291,4 +5487,1083 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Prince Central 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 834呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (4+房)
+$6008万
+$44,474/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 869呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 685呎 (3房)
+$2460万
+$35,907/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (4+房)
+$3218万
+$36,154/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 871呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (1房)
+$1075万
+$31,255/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 891呎 (4+房)
+$3150万
+$35,354/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1388万
+$31,838/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$1148万
+$37,901/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1283万
+$37,181/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 254呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>F | 624呎 (3房)
+$2642万
+$42,335/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>G | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$971万
+$31,950/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1258万
+$36,452/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 254呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>F | 624呎 (3房)
+$2587万
+$41,460/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>G | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1312万
+$30,095/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$962万
+$31,739/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1060万
+$30,738/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 254呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 624呎 (3房)
+$2132万
+$34,173/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>G | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1302万
+$29,855/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$946万
+$31,106/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1229万
+$35,632/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>E | 254呎 (开放式)
+$941万
+$37,051/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 624呎 (3房)
+$2062万
+$33,049/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>G | 266呎 (开放式)
+$973万
+$36,594/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1362万
+$31,238/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$924万
+$30,401/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1204万
+$34,899/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$899万
+$35,805/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1032万
+$30,527/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1042万
+$30,301/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$956万
+$35,955/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1506万
+$34,534/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$896万
+$29,573/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1198万
+$34,728/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$890万
+$35,462/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1204万
+$35,630/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1034万
+$30,059/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$949万
+$35,669/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1273万
+$29,208/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$893万
+$29,461/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1191万
+$34,522/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$880万
+$35,052/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1201万
+$35,527/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1213万
+$35,262/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$941万
+$35,383/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1498万
+$34,362/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$893万
+$29,461/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1191万
+$34,522/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$880万
+$35,052/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1201万
+$35,527/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 343呎 (1房)
+$1031万
+$30,060/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$941万
+$35,383/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1483万
+$34,021/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$886万
+$29,239/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1184万
+$34,316/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$858万
+$34,195/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1015万
+$30,017/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1206万
+$35,047/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$928万
+$34,887/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1476万
+$33,851/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$883万
+$29,141/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1176万
+$34,099/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$847万
+$33,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1190万
+$35,207/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 343呎 (1房)
+$1022万
+$29,787/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$921万
+$34,639/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 436呎 (2房)
+$1468万
+$33,679/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$880万
+$29,043/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>D | 345呎 (1房)
+$1174万
+$34,029/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$829万
+$33,032/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1165万
+$34,462/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1176万
+$34,198/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$893万
+$33,564/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 274呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 283呎 (1房)
+$1103万
+$38,965/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 251呎 (开放式)
+$817万
+$32,562/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>F | 338呎 (1房)
+$1150万
+$34,012/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>G | 344呎 (1房)
+$1161万
+$33,750/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>H | 266呎 (开放式)
+$919万
+$34,538/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -670,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -730,6 +734,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -776,6 +800,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>60084800</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>44474</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -826,6 +866,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -872,6 +932,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>32177500</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>36154</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -918,6 +994,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>24596400</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>35907</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -968,6 +1060,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1014,6 +1126,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>31500000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>35354</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1060,6 +1188,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10751600</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>31255</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1110,6 +1254,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1160,6 +1324,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1210,6 +1394,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1256,6 +1460,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>25096150</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>40218</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1306,6 +1526,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1352,6 +1592,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>12186144</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>35322</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1398,6 +1654,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>10909800</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>36006</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,6 +1720,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1494,6 +1786,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>13881480</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>31838</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1544,6 +1852,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1590,6 +1918,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>24577450</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>39387</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1640,6 +1984,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1686,6 +2050,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>11947200</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>34630</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1732,6 +2112,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>9712900</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>31950</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1782,6 +2178,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1832,6 +2248,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1882,6 +2318,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1928,6 +2384,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>21323900</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>34173</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1978,6 +2450,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2024,6 +2516,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>10604600</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>30738</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2070,6 +2578,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9616900</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>31739</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2120,6 +2644,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2166,6 +2710,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>13121400</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>30095</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2212,6 +2772,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9247300</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>34764</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2258,6 +2834,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>20622700</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>33049</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2304,6 +2896,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>8940450</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>35199</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2350,6 +2958,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>11678350</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>33850</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2396,6 +3020,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>9456200</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>31106</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2446,6 +3086,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2492,6 +3152,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>13016900</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>29855</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2538,6 +3214,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>9085800</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>34157</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2584,6 +3276,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>10423500</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>30301</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2630,6 +3338,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>10318100</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>30527</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2676,6 +3400,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8537650</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>34015</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2722,6 +3462,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>11438000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>33154</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2768,6 +3524,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>9242000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>30401</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2818,6 +3590,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2864,6 +3656,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>13619700</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>31238</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2910,6 +3718,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>9013600</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>33886</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2956,6 +3780,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>10340200</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>30059</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3002,6 +3842,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>11440850</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>33849</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3048,6 +3904,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>8455950</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>33689</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3094,6 +3966,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>11381950</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>32991</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3140,6 +4028,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8960700</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>29573</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3190,6 +4094,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3236,6 +4160,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>14304150</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>32808</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3282,6 +4222,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>8941400</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>33614</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3328,6 +4284,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>11523500</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>33499</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3374,6 +4346,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>11407600</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3420,6 +4408,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>8358100</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>33299</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3466,6 +4470,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>11314500</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>32796</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3512,6 +4532,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>8926700</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>29461</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3562,6 +4598,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3608,6 +4664,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>12734700</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>29208</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4726,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8941400</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>33614</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3700,6 +4788,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>10310500</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>30060</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3746,6 +4850,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>11407600</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3792,6 +4912,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>8358100</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>33299</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3838,6 +4974,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>11314500</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>32796</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3884,6 +5036,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>8926700</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>29461</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3934,6 +5102,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3980,6 +5168,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>14232900</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>32644</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4026,6 +5230,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>8816000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>33143</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4072,6 +5292,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>11453200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>33294</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4118,6 +5354,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>10145600</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>30017</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4164,6 +5416,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>8153850</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>32485</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4210,6 +5478,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>11247050</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4256,6 +5540,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>8859500</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>29239</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4306,6 +5606,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4352,6 +5672,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>14091350</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>32320</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4398,6 +5734,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>8753300</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>32907</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4444,6 +5796,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>10217000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>29787</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4490,6 +5858,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>11305000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>33447</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4536,6 +5920,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8042700</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>32043</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4582,6 +5982,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>11175800</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>32394</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4628,6 +6044,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>8829800</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>29141</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,6 +6110,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4724,6 +6176,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>14021050</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>32158</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4770,6 +6238,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>8481600</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>31886</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4816,6 +6300,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>11175800</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>32488</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4862,6 +6362,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>11065600</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>32738</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4908,6 +6424,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7876450</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>31380</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,6 +6486,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>11153000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>32328</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5000,6 +6548,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>29043</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5050,6 +6614,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5096,6 +6680,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>13949800</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>31995</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5142,6 +6742,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>8727650</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>32811</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5188,6 +6804,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>11029500</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>32062</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5234,6 +6866,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>10921200</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>32311</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5280,6 +6928,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>7764350</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>30934</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5330,6 +6994,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5376,6 +7060,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>10475650</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>37016</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5426,6 +7126,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5476,13 +7196,33 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5646,7 +7386,7 @@
           <t>B | 1351呎 (4+房)
 $6008万
 $44,474/呎
-(22年-07月)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr"/>
@@ -5675,7 +7415,7 @@
           <t>B | 685呎 (3房)
 $2460万
 $35,907/呎
-(23年-03月)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -5683,7 +7423,7 @@
           <t>C | 890呎 (4+房)
 $3218万
 $36,154/呎
-(22年-07月)</t>
+(22年-07月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
@@ -5719,7 +7459,7 @@
           <t>C | 344呎 (1房)
 $1075万
 $31,255/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -5727,7 +7467,7 @@
           <t>D | 891呎 (4+房)
 $3150万
 $35,354/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -5746,7 +7486,7 @@
           <t>A | 436呎 (2房)
 $1388万
 $31,838/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -5826,7 +7566,7 @@
           <t>C | 304呎 (1房)
 $971万
 $31,950/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -5874,7 +7614,7 @@
           <t>A | 436呎 (2房)
 $1312万
 $30,095/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -5890,7 +7630,7 @@
           <t>C | 303呎 (1房)
 $962万
 $31,739/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -5898,7 +7638,7 @@
           <t>D | 345呎 (1房)
 $1060万
 $30,738/呎
-(22年-07月)</t>
+(22年-07月-12日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -5914,7 +7654,7 @@
           <t>F | 624呎 (3房)
 $2132万
 $34,173/呎
-(22年-06月)</t>
+(22年-06月-28日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -5938,7 +7678,7 @@
           <t>A | 436呎 (2房)
 $1302万
 $29,855/呎
-(22年-06月)</t>
+(22年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -5954,7 +7694,7 @@
           <t>C | 304呎 (1房)
 $946万
 $31,106/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5978,7 +7718,7 @@
           <t>F | 624呎 (3房)
 $2062万
 $33,049/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -6002,7 +7742,7 @@
           <t>A | 436呎 (2房)
 $1362万
 $31,238/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -6018,7 +7758,7 @@
           <t>C | 304呎 (1房)
 $924万
 $30,401/呎
-(23年-05月)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -6042,7 +7782,7 @@
           <t>F | 338呎 (1房)
 $1032万
 $30,527/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -6050,7 +7790,7 @@
           <t>G | 344呎 (1房)
 $1042万
 $30,301/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
@@ -6089,7 +7829,7 @@
           <t>C | 303呎 (1房)
 $896万
 $29,573/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -6121,7 +7861,7 @@
           <t>G | 344呎 (1房)
 $1034万
 $30,059/呎
-(22年-06月)</t>
+(22年-06月-19日)</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -6144,7 +7884,7 @@
           <t>A | 436呎 (2房)
 $1273万
 $29,208/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -6160,7 +7900,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -6231,7 +7971,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -6263,7 +8003,7 @@
           <t>G | 343呎 (1房)
 $1031万
 $30,060/呎
-(22年-11月)</t>
+(22年-11月-16日)</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
@@ -6302,7 +8042,7 @@
           <t>C | 303呎 (1房)
 $886万
 $29,239/呎
-(22年-07月)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -6326,7 +8066,7 @@
           <t>F | 338呎 (1房)
 $1015万
 $30,017/呎
-(22年-07月)</t>
+(22年-07月-10日)</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -6373,7 +8113,7 @@
           <t>C | 303呎 (1房)
 $883万
 $29,141/呎
-(22年-07月)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -6405,7 +8145,7 @@
           <t>G | 343呎 (1房)
 $1022万
 $29,787/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -6444,7 +8184,7 @@
           <t>C | 303呎 (1房)
 $880万
 $29,043/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -7386,7 +7386,7 @@
           <t>B | 1351呎 (4+房)
 $6008万
 $44,474/呎
-(22年-07月-04日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
           <t>B | 685呎 (3房)
 $2460万
 $35,907/呎
-(23年-03月-23日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -7423,7 +7423,7 @@
           <t>C | 890呎 (4+房)
 $3218万
 $36,154/呎
-(22年-07月-19日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
           <t>C | 344呎 (1房)
 $1075万
 $31,255/呎
-(24年-07月-10日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>D | 891呎 (4+房)
 $3150万
 $35,354/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
           <t>A | 436呎 (2房)
 $1388万
 $31,838/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -7566,7 +7566,7 @@
           <t>C | 304呎 (1房)
 $971万
 $31,950/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>A | 436呎 (2房)
 $1312万
 $30,095/呎
-(23年-12月-10日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -7630,7 +7630,7 @@
           <t>C | 303呎 (1房)
 $962万
 $31,739/呎
-(22年-06月-23日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -7638,7 +7638,7 @@
           <t>D | 345呎 (1房)
 $1060万
 $30,738/呎
-(22年-07月-12日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -7654,7 +7654,7 @@
           <t>F | 624呎 (3房)
 $2132万
 $34,173/呎
-(22年-06月-28日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -7678,7 +7678,7 @@
           <t>A | 436呎 (2房)
 $1302万
 $29,855/呎
-(22年-06月-29日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -7694,7 +7694,7 @@
           <t>C | 304呎 (1房)
 $946万
 $31,106/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7718,7 +7718,7 @@
           <t>F | 624呎 (3房)
 $2062万
 $33,049/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -7742,7 +7742,7 @@
           <t>A | 436呎 (2房)
 $1362万
 $31,238/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>C | 304呎 (1房)
 $924万
 $30,401/呎
-(23年-05月-17日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -7782,7 +7782,7 @@
           <t>F | 338呎 (1房)
 $1032万
 $30,527/呎
-(22年-06月-16日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>G | 344呎 (1房)
 $1042万
 $30,301/呎
-(22年-06月-16日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
@@ -7829,7 +7829,7 @@
           <t>C | 303呎 (1房)
 $896万
 $29,573/呎
-(22年-06月-16日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -7861,7 +7861,7 @@
           <t>G | 344呎 (1房)
 $1034万
 $30,059/呎
-(22年-06月-19日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -7884,7 +7884,7 @@
           <t>A | 436呎 (2房)
 $1273万
 $29,208/呎
-(22年-06月-23日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -7900,7 +7900,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-21日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -7971,7 +7971,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-16日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -8003,7 +8003,7 @@
           <t>G | 343呎 (1房)
 $1031万
 $30,060/呎
-(22年-11月-16日)</t>
+(22年-11月)</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
@@ -8042,7 +8042,7 @@
           <t>C | 303呎 (1房)
 $886万
 $29,239/呎
-(22年-07月-27日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -8066,7 +8066,7 @@
           <t>F | 338呎 (1房)
 $1015万
 $30,017/呎
-(22年-07月-10日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -8113,7 +8113,7 @@
           <t>C | 303呎 (1房)
 $883万
 $29,141/呎
-(22年-07月-04日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -8145,7 +8145,7 @@
           <t>G | 343呎 (1房)
 $1022万
 $29,787/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -8184,7 +8184,7 @@
           <t>C | 303呎 (1房)
 $880万
 $29,043/呎
-(22年-06月-23日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -7386,7 +7386,7 @@
           <t>B | 1351呎 (4+房)
 $6008万
 $44,474/呎
-(22年-07月)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
           <t>B | 685呎 (3房)
 $2460万
 $35,907/呎
-(23年-03月)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -7423,7 +7423,7 @@
           <t>C | 890呎 (4+房)
 $3218万
 $36,154/呎
-(22年-07月)</t>
+(22年-07月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
           <t>C | 344呎 (1房)
 $1075万
 $31,255/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>D | 891呎 (4+房)
 $3150万
 $35,354/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
           <t>A | 436呎 (2房)
 $1388万
 $31,838/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -7566,7 +7566,7 @@
           <t>C | 304呎 (1房)
 $971万
 $31,950/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>A | 436呎 (2房)
 $1312万
 $30,095/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -7630,7 +7630,7 @@
           <t>C | 303呎 (1房)
 $962万
 $31,739/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -7638,7 +7638,7 @@
           <t>D | 345呎 (1房)
 $1060万
 $30,738/呎
-(22年-07月)</t>
+(22年-07月-12日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -7654,7 +7654,7 @@
           <t>F | 624呎 (3房)
 $2132万
 $34,173/呎
-(22年-06月)</t>
+(22年-06月-28日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -7678,7 +7678,7 @@
           <t>A | 436呎 (2房)
 $1302万
 $29,855/呎
-(22年-06月)</t>
+(22年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -7694,7 +7694,7 @@
           <t>C | 304呎 (1房)
 $946万
 $31,106/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7718,7 +7718,7 @@
           <t>F | 624呎 (3房)
 $2062万
 $33,049/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -7742,7 +7742,7 @@
           <t>A | 436呎 (2房)
 $1362万
 $31,238/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>C | 304呎 (1房)
 $924万
 $30,401/呎
-(23年-05月)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -7782,7 +7782,7 @@
           <t>F | 338呎 (1房)
 $1032万
 $30,527/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>G | 344呎 (1房)
 $1042万
 $30,301/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
@@ -7829,7 +7829,7 @@
           <t>C | 303呎 (1房)
 $896万
 $29,573/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -7861,7 +7861,7 @@
           <t>G | 344呎 (1房)
 $1034万
 $30,059/呎
-(22年-06月)</t>
+(22年-06月-19日)</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -7884,7 +7884,7 @@
           <t>A | 436呎 (2房)
 $1273万
 $29,208/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -7900,7 +7900,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -7971,7 +7971,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -8003,7 +8003,7 @@
           <t>G | 343呎 (1房)
 $1031万
 $30,060/呎
-(22年-11月)</t>
+(22年-11月-16日)</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
@@ -8042,7 +8042,7 @@
           <t>C | 303呎 (1房)
 $886万
 $29,239/呎
-(22年-07月)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -8066,7 +8066,7 @@
           <t>F | 338呎 (1房)
 $1015万
 $30,017/呎
-(22年-07月)</t>
+(22年-07月-10日)</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -8113,7 +8113,7 @@
           <t>C | 303呎 (1房)
 $883万
 $29,141/呎
-(22年-07月)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -8145,7 +8145,7 @@
           <t>G | 343呎 (1房)
 $1022万
 $29,787/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -8184,7 +8184,7 @@
           <t>C | 303呎 (1房)
 $880万
 $29,043/呎
-(22年-06月)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
